--- a/docs/deliverables/out/Drop-1_Transactional/BRD-09_Customer_Servicing_Facility/BIBS_TestPlan_BRD-09_Customer_Servicing_Facility_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-09_Customer_Servicing_Facility/BIBS_TestPlan_BRD-09_Customer_Servicing_Facility_v1.0.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$120</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>10</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-9 Customer Servicing Facility. 17 FRs, 29 BRD IDs, 82 test conditions, 8 scenarios, 116 test cases (63 positive, 53 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-9 (FRS_BRD09_CUSTOMER_SERVICING_FACILITY.md). 17 FRs, 29 BRD IDs, 82 test conditions, 8 scenarios, 116 test cases (63 positive, 53 negative), 0 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,310 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-001</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The FRS messages "Invalid user ID or password" and "Your account is locked. Contact the System Administrator" differ from the platform log-in that BRD-9 reuses (fit FIT), which shows "Invalid user name or password" and "Account is locked. Contact your administrator." Acceptance criterion 3 repeats FR-CSF-002.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Quote the platform texts in FRS v1.1, as FRS BRD-11 FR-UA-001 does; the cases use the platform texts. Keep criterion 3 in FR-CSF-002 only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-010</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>The response target "within 3 seconds (p.13)" gives no load: number of clients and accounts, concurrent agents. The FRS does not say whether a name search matches the start of the name, any word, or ignores accents and case.</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>State the measurement load (24 concurrent users, the year-5 volume of section 8) and the name-matching rule; the cases time searches in the peak window on SIT data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-012</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>The mapping list CSF_STATUS_MAP has no rule for an account stage that no row matches, or for two rows that match the same account. A cancelled account with premium outstanding could match Booked and Closed.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>State that the first row by order wins and that an unmatched stage shows a fixed value (for example "Other") with an alert to the list owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-020</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>The checks are Yes / No, so a check the agent did not ask cannot be recorded; "Record the result of the verification checks" does not say whether all four or only one must be answered. Whether a verification is also needed before a resend is open (CSQ03), and it is not stated whether a PASSED verification belongs to the agent or to any agent of the client.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Add a value "Not asked", state how many checks must be answered, and tie the verification to the agent and client. The cases assume all four are answered and the verification is per agent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-021</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>"Add" contact details depends on CSQ15 and cannot be tested; "Philippine mobile format" is not defined (09xxxxxxxxx, +639xxxxxxxxx or both); the phone rule "digits and separators" has no length.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Define the accepted mobile and phone formats with examples and remove "add" until CSQ15 is answered; the cases use 12345 as an invalid mobile only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-022</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Acceptance covers only the disabled sync. The sending, the number and interval of retries and the FAILED state cannot be tested until the interface is specified (CSQ01).</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Give the retry count and interval as parameters; TC-CSF-022.3-01 and 3-02 stay Blocked until a test stub of the interface exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-030</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>The RA password convention (CSQ06) is open, so the cases can check only that the file needs a password and that the password arrives separately, not its value.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Add the password rule to FR-CSF-030 when CSQ06 is answered; the cases are then extended with the expected password.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-032</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>The maximum file size (CSQ08) is not given, so the "too large" boundary cannot be set; the 5-second upload target has no file size.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>State the size limit and the file size for the 5-second target; until then the test uses the platform limit and a 2 MB file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-09</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-033</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>The permissions matrix gives CSF_MANAGEMENT the Servicing View (CSF_VIEW) but not ATTACHMENT_VIEW. The FRS does not say whether management sees the Documents, Renewal Advice and E-policies tabs as a list without download, or not at all.</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>State the behaviour for management in section 3.3; the access checks assume the lists are shown and opening a document is refused.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>TF-CSF-10</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>FR-CSF-043</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>The requirement is an infrastructure control and has no screen; the BRD's 4-hour RPO and backup (retention table) conflict with the 15-minute backup (CSQ11).</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Keep FR-CSF-043 for the infrastructure team's evidence (restore test log) and record the CSQ11 answer; the cases are run by the infrastructure team and witnessed by QA.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D514">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-9 Customer Servicing Facility&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2079,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2168,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2203,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2221,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2243,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2261,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2279,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2292,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2315,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2333,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2351,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2369,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2387,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2405,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2423,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2441,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2472,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2499,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2517,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2535,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2548,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2566,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2589,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2607,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2625,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2643,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2661,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2679,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2719,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2737,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2759,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3006,7 +2574,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Internal draft from FRS BRD-9 v1.0 and the Customer Servicing build design</t>
+          <t>Internal draft from FRS BRD-9 v1.0</t>
         </is>
       </c>
     </row>
@@ -3347,7 +2915,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>A direct call without the permission is refused and the refusal is logged.</t>
+          <t>A direct request without the permission is refused and the refusal is logged.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -3891,7 +3459,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>A change to the mapping list changes the displayed status without a new build, and the change is audited.</t>
+          <t>A change to the mapping list changes the displayed status without a change to the system, and the change is audited.</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -4819,7 +4387,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>An account without a confirmed e-policy offers no resend, and a direct call is refused.</t>
+          <t>An account without a confirmed e-policy offers no resend, and a direct request is refused.</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -6131,7 +5699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R120"/>
+  <dimension ref="A1:Q120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6146,12 +5714,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6186,7 +5753,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -6251,32 +5817,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -6323,7 +5884,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -6342,16 +5903,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -6396,7 +5956,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -6414,16 +5974,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -6468,7 +6027,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -6487,16 +6046,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -6541,7 +6099,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -6561,16 +6119,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -6615,7 +6172,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -6634,16 +6191,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -6689,7 +6245,7 @@
       <c r="I10" s="12" t="inlineStr">
         <is>
           <t>agent2 is locked (TC-CSF-001.3-01).
-Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -6708,16 +6264,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -6762,14 +6317,14 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
           <t>1. Log in as ao.
 2. Open the side menu.
-3. Type the address /csf in the browser.</t>
+3. Open the address of the Customer Service Facility directly in the browser.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -6782,16 +6337,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -6837,7 +6391,7 @@
       <c r="I12" s="12" t="inlineStr">
         <is>
           <t>Cases TC-CSF-001.1-01 and TC-CSF-001.2-01 ran today.
-Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-01 Test users per role; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -6855,16 +6409,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -6928,16 +6481,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -7001,16 +6553,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -7035,7 +6586,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Agent calls the resend to another address directly</t>
+          <t>Agent sends a resend to another address directly</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -7050,7 +6601,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -7060,14 +6611,14 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as agent1 and take the token.
+          <t>1. Sign in as agent1.
 2. Call the resend of an RA of TD-CSF-06 with a recipient other than the registered e-mail.
 3. Log in as the System Administrator and open Administration &gt; Audit Trail.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>The call returns HTTP 403 and nothing is sent. The audit trail shows the refused call with user, endpoint and time.
+          <t>The request is refused and nothing is sent. The audit trail shows the refused request with the user and time.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -7076,16 +6627,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -7110,7 +6660,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Management calls the contact update directly</t>
+          <t>Management sends a contact update directly</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -7125,7 +6675,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -7135,13 +6685,13 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as mgmt1 and take the token.
+          <t>1. Sign in as mgmt1.
 2. Call the contact update of TD-CSF-02 with a new mobile number.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>The call returns HTTP 403; the client's mobile number is unchanged.
+          <t>The request is refused; the client's mobile number is unchanged.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -7150,16 +6700,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -7224,16 +6773,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -7297,16 +6845,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -7369,16 +6916,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -7441,16 +6987,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -7514,16 +7059,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -7587,16 +7131,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -7659,16 +7202,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -7731,16 +7273,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -7804,16 +7345,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -7877,16 +7417,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -7950,16 +7489,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -8023,16 +7561,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -8095,16 +7632,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -8168,16 +7704,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -8241,16 +7776,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -8314,16 +7848,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr"/>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -8386,16 +7919,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -8440,7 +7972,7 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>The test lead stops the invoice ledger service on SIT for the test (or blocks its query endpoint).
+          <t>The test lead makes the invoice ledger unavailable on SIT for the test.
 Data: TD-CSF-02 Client with CBG and non-CBG accounts</t>
         </is>
       </c>
@@ -8461,16 +7993,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -8534,16 +8065,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -8594,7 +8124,7 @@
       <c r="J36" s="12" t="inlineStr">
         <is>
           <t>1. As agent1, open the Servicing View of TD-CSF-02 and look for Open client page.
-2. Type the client page address /crm/clients/{id}.</t>
+2. Type the address of the full client page of the client.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -8607,16 +8137,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -8680,16 +8209,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -8752,16 +8280,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -8824,16 +8351,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -8896,16 +8422,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -8962,7 +8487,7 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>The account shows Awaiting without a new build; the audit trail shows the row change with old and new value and the user.</t>
+          <t>The account shows Awaiting without a change to the system; the audit trail shows the row change with old and new value and the user.</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
@@ -8970,16 +8495,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -9042,16 +8566,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -9114,16 +8637,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -9186,16 +8708,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr"/>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -9258,16 +8779,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -9330,16 +8850,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -9402,16 +8921,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -9475,16 +8993,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -9529,7 +9046,7 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
@@ -9548,16 +9065,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -9602,7 +9118,7 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
@@ -9620,16 +9136,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -9674,7 +9189,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
@@ -9693,16 +9208,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -9747,7 +9261,7 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
@@ -9766,16 +9280,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -9820,7 +9333,7 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
@@ -9839,16 +9352,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -9894,7 +9406,7 @@
       <c r="I54" s="12" t="inlineStr">
         <is>
           <t>A PASSED verification of TD-CSF-02 was recorded 29 minutes ago (the test lead sets the time in the test database, or the tester waits).
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
@@ -9912,16 +9424,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -9967,7 +9478,7 @@
       <c r="I55" s="12" t="inlineStr">
         <is>
           <t>A PASSED verification of TD-CSF-02 was recorded 31 minutes ago.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -9986,16 +9497,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr"/>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -10040,7 +9550,7 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
@@ -10059,16 +9569,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -10114,7 +9623,7 @@
       <c r="I57" s="12" t="inlineStr">
         <is>
           <t>No failed verification of "UAT CSF Client Two" today.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -10133,16 +9642,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr"/>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -10188,7 +9696,7 @@
       <c r="I58" s="12" t="inlineStr">
         <is>
           <t>A PASSED verification of TD-CSF-02 younger than 30 minutes.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
@@ -10207,16 +9715,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -10262,7 +9769,7 @@
       <c r="I59" s="12" t="inlineStr">
         <is>
           <t>A PASSED verification of TD-CSF-02.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -10280,16 +9787,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr"/>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -10329,18 +9835,18 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
           <t>No verification of UAT CSF Client Two today.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>1. Call the contact update of UAT CSF Client Two with a new mobile number using agent1's token.</t>
+          <t>1. Call the contact update of UAT CSF Client Two with a new mobile number signed in as agent1.</t>
         </is>
       </c>
       <c r="K60" s="12" t="inlineStr">
@@ -10354,16 +9860,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr"/>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -10403,13 +9908,13 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
           <t>A PASSED verification of TD-CSF-02.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
@@ -10428,16 +9933,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -10482,7 +9986,7 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr">
@@ -10500,16 +10004,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr"/>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -10554,7 +10057,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -10573,16 +10076,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -10627,7 +10129,7 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr">
@@ -10646,16 +10148,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr"/>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -10700,7 +10201,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
@@ -10719,16 +10220,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr"/>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -10774,7 +10274,7 @@
       <c r="I66" s="12" t="inlineStr">
         <is>
           <t>TC-CSF-021.1-01 is done.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
@@ -10793,16 +10293,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr"/>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -10848,7 +10347,7 @@
       <c r="I67" s="12" t="inlineStr">
         <is>
           <t>TC-CSF-021.1-02 is done.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
@@ -10866,16 +10365,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -10921,7 +10419,7 @@
       <c r="I68" s="12" t="inlineStr">
         <is>
           <t>CSF_LEGACY_SYNC_ENABLED is false; TC-CSF-021.1-01 is done.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
@@ -10939,16 +10437,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -10993,7 +10490,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
@@ -11012,16 +10509,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr"/>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -11066,7 +10562,7 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
@@ -11084,16 +10580,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr"/>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -11138,8 +10633,8 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>A test stub of the QPS / EBIX interface is available on SIT (only after BDOI specifies it, CSQ01); CSF_LEGACY_SYNC_ENABLED set to true.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>A test interface of QPS / EBIX is available on SIT (only after BDOI specifies it, CSQ01); CSF_LEGACY_SYNC_ENABLED set to true.
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -11150,7 +10645,7 @@
       </c>
       <c r="K71" s="12" t="inlineStr">
         <is>
-          <t>The change moves from Queued to Sent for QPS and EBIX; the stub received the payload.</t>
+          <t>The change moves from Queued to Sent for QPS and EBIX; the test interface received the change.</t>
         </is>
       </c>
       <c r="L71" s="12" t="inlineStr">
@@ -11158,16 +10653,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -11212,8 +10706,8 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>As the case before; the stub is stopped.
-Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>As the case before; the test interface is stopped.
+Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -11232,16 +10726,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr"/>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -11286,7 +10779,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as delivered</t>
+          <t>Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -11304,16 +10797,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr"/>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -11376,16 +10868,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr"/>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -11448,16 +10939,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -11521,16 +11011,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr"/>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -11593,16 +11082,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr"/>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -11665,16 +11153,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -11738,16 +11225,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -11811,16 +11297,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -11885,16 +11370,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr"/>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -11959,16 +11443,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -12032,16 +11515,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -12104,16 +11586,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -12138,7 +11619,7 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Direct resend call for an account without a confirmed e-policy</t>
+          <t>Direct resend request for an account without a confirmed e-policy</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -12153,7 +11634,7 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
@@ -12163,12 +11644,12 @@
       </c>
       <c r="J85" s="12" t="inlineStr">
         <is>
-          <t>1. Call the e-policy resend of that account with agent1's token.</t>
+          <t>1. Call the e-policy resend of that account signed in as agent1.</t>
         </is>
       </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
-          <t>The call is refused and nothing is sent.
+          <t>The request is refused and nothing is sent.
 Message "The account has no confirmed e-policy".</t>
         </is>
       </c>
@@ -12177,16 +11658,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -12249,16 +11729,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -12321,16 +11800,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -12393,16 +11871,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -12465,16 +11942,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -12537,16 +12013,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -12610,16 +12085,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -12683,16 +12157,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -12756,16 +12229,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -12829,16 +12301,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -12902,16 +12373,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -12975,16 +12445,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -13035,12 +12504,12 @@
       <c r="J97" s="12" t="inlineStr">
         <is>
           <t>1. As mgmt1 open the Documents tab of TD-CSF-02.
-2. Call the attachment upload for the client with mgmt1's token.</t>
+2. Call the attachment upload for the client signed in as mgmt1.</t>
         </is>
       </c>
       <c r="K97" s="12" t="inlineStr">
         <is>
-          <t>No Upload button; the call returns HTTP 403.
+          <t>No Upload button; the request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -13049,16 +12518,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -13121,16 +12589,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr"/>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -13193,16 +12660,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -13266,16 +12732,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -13326,12 +12791,12 @@
       <c r="J101" s="12" t="inlineStr">
         <is>
           <t>1. Look for the restricted document of TD-CSF-08 on the Documents tab.
-2. Call the attachment download of that document with agent1's token.</t>
+2. Call the attachment download of that document signed in as agent1.</t>
         </is>
       </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
-          <t>The document is not listed; the call returns HTTP 403.
+          <t>The document is not listed; the request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -13340,16 +12805,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -13414,16 +12878,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr"/>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -13486,16 +12949,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr"/>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -13559,16 +13021,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -13632,16 +13093,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -13692,12 +13152,12 @@
       <c r="J106" s="12" t="inlineStr">
         <is>
           <t>1. As the System Administrator open an audit row; look for edit and delete actions.
-2. Try an update and a delete of the row through the API.</t>
+2. Try an update and a delete of the row by a direct request.</t>
         </is>
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>No edit or delete action is offered; the API has no update or delete of audit rows and the calls are refused.</t>
+          <t>No edit or delete action is offered; audit rows cannot be updated or deleted and direct requests are refused.</t>
         </is>
       </c>
       <c r="L106" s="12" t="inlineStr">
@@ -13705,16 +13165,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr"/>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -13778,16 +13237,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr"/>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -13850,16 +13308,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -13923,16 +13380,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -13983,12 +13439,12 @@
       <c r="J110" s="12" t="inlineStr">
         <is>
           <t>1. As agent1 open Reports and Administration.
-2. Call the run of CSF-CONTACT-CHANGES with agent1's token.</t>
+2. Call the run of CSF-CONTACT-CHANGES signed in as agent1.</t>
         </is>
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>The Customer Service category and the Audit Trail are not offered; the call returns HTTP 403.
+          <t>The Customer Service category and the Audit Trail are not offered; the request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -13997,16 +13453,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr"/>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -14070,16 +13525,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr"/>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -14143,16 +13597,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -14215,16 +13668,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -14275,12 +13727,12 @@
       <c r="J114" s="12" t="inlineStr">
         <is>
           <t>1. Search System Parameters and Scheduled Jobs for a CSF activity log setting.
-2. Try an update and a delete of an activity row through the API.</t>
+2. Try an update and a delete of an activity row by a direct request.</t>
         </is>
       </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>No parameter or job disables the log; the API offers no update or delete and the calls are refused.</t>
+          <t>No parameter or job disables the log; no update or delete is offered and direct requests are refused.</t>
         </is>
       </c>
       <c r="L114" s="12" t="inlineStr">
@@ -14288,16 +13740,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr"/>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -14361,16 +13812,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -14420,12 +13870,12 @@
       </c>
       <c r="J116" s="12" t="inlineStr">
         <is>
-          <t>1. As agent1 call the run of CSF-ACTIVITY.</t>
+          <t>1. As agent1 send a direct request to run CSF-ACTIVITY.</t>
         </is>
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>The call returns HTTP 403.
+          <t>The request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -14434,16 +13884,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr"/>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -14489,13 +13938,13 @@
       <c r="I117" s="12" t="inlineStr"/>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>1. Read the database setting archive_timeout and the backup schedule.
+          <t>1. Read the archive interval of the database and the backup schedule.
 2. List the archived log segments of the last two hours.</t>
         </is>
       </c>
       <c r="K117" s="12" t="inlineStr">
         <is>
-          <t>archive_timeout is 15 minutes or less; at least one segment is archived in every 15-minute window; the daily base backup runs outside 10:00-12:00 and 14:00-16:00.</t>
+          <t>The archive interval is 15 minutes or less; at least one segment is archived in every 15-minute window; the daily base backup runs outside 10:00-12:00 and 14:00-16:00.</t>
         </is>
       </c>
       <c r="L117" s="12" t="inlineStr">
@@ -14503,16 +13952,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -14573,16 +14021,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr"/>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -14641,16 +14088,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr"/>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -14709,23 +14155,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr"/>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R120"/>
+  <autoFilter ref="A4:Q120"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N620">
+  <conditionalFormatting sqref="M5:M620">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -14739,19 +14184,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R620">
+  <conditionalFormatting sqref="A5:Q620">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F620" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L620" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N620" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M620" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -14775,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14787,7 +14232,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -14814,7 +14258,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -14859,11 +14302,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -14901,10 +14339,7 @@
       <c r="H5" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -14943,10 +14378,7 @@
       <c r="H6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -14985,10 +14417,7 @@
       <c r="H7" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15027,10 +14456,7 @@
       <c r="H8" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15069,10 +14495,7 @@
       <c r="H9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15111,10 +14534,7 @@
       <c r="H10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15153,10 +14573,7 @@
       <c r="H11" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15195,10 +14612,7 @@
       <c r="H12" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15237,10 +14651,7 @@
       <c r="H13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15279,10 +14690,7 @@
       <c r="H14" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15321,10 +14729,7 @@
       <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15363,10 +14768,7 @@
       <c r="H16" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15405,10 +14807,7 @@
       <c r="H17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15447,10 +14846,7 @@
       <c r="H18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15489,10 +14885,7 @@
       <c r="H19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15531,10 +14924,7 @@
       <c r="H20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15573,10 +14963,7 @@
       <c r="H21" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15611,10 +14998,7 @@
       <c r="H22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15649,10 +15033,7 @@
       <c r="H23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15687,10 +15068,7 @@
       <c r="H24" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15725,10 +15103,7 @@
       <c r="H25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15763,10 +15138,7 @@
       <c r="H26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15801,10 +15173,7 @@
       <c r="H27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15839,10 +15208,7 @@
       <c r="H28" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15877,10 +15243,7 @@
       <c r="H29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15915,10 +15278,7 @@
       <c r="H30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15953,10 +15313,7 @@
       <c r="H31" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15991,10 +15348,7 @@
       <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16029,10 +15383,7 @@
       <c r="H33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16067,10 +15418,7 @@
       <c r="H34" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16105,10 +15453,7 @@
       <c r="H35" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16143,10 +15488,7 @@
       <c r="H36" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16181,10 +15523,7 @@
       <c r="H37" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16219,10 +15558,7 @@
       <c r="H38" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16257,10 +15593,7 @@
       <c r="H39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16295,10 +15628,7 @@
       <c r="H40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16333,10 +15663,7 @@
       <c r="H41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16371,10 +15698,7 @@
       <c r="H42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16409,10 +15733,7 @@
       <c r="H43" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16447,10 +15768,7 @@
       <c r="H44" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16485,10 +15803,7 @@
       <c r="H45" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16523,10 +15838,7 @@
       <c r="H46" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16561,10 +15873,7 @@
       <c r="H47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16599,10 +15908,7 @@
       <c r="H48" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16637,10 +15943,7 @@
       <c r="H49" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16675,32 +15978,29 @@
       <c r="H50" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J50"/>
+  <autoFilter ref="A4:I50"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J550">
+  <conditionalFormatting sqref="I5:I550">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J550">
+  <conditionalFormatting sqref="A5:I550">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J550" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I550" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -16795,12 +16095,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>One user per role - agent1 and agent2 (CSF_AGENT), sup1 (CSF_SUPERVISOR), mgmt1 (CSF_MANAGEMENT), the System Administrator, ao (MKT_AO, no CSF role). The build design plans the SIT/UAT users csfagent, csfagent2, csfsup and csfmgmt for the same roles.</t>
+          <t>One user per role - agent1 and agent2 (CSF_AGENT), sup1 (CSF_SUPERVISOR), mgmt1 (CSF_MANAGEMENT), the System Administrator, ao (MKT_AO, no CSF role). The seed data adds the SIT/UAT users csfagent, csfagent2, csfsup and csfmgmt for the same roles.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Created by the test lead through User Access requests on SIT; planned seed V1940 of the build design</t>
+          <t>Created by the test lead through User Access requests on SIT, or the seed users</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -16825,7 +16125,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Prepared by the test lead on SIT from masked seed clients (V981) and accounts keyed in the BRD-1 screens</t>
+          <t>Prepared by the test lead on SIT from masked seed clients and accounts keyed in the BRD-1 screens</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -16990,7 +16290,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Parameters as delivered</t>
+          <t>Parameters as configured</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -17000,7 +16300,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Configuration delivered with the build (FRS section 9.1)</t>
+          <t>Configuration of the SIT environment (FRS section 9.1)</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -17062,7 +16362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17072,12 +16372,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -17107,7 +16406,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -17147,32 +16445,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -17212,16 +16505,15 @@
           <t>The Customer Search is the landing page and clients open in the Servicing View.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -17259,16 +16551,15 @@
           <t>The Customer Search is the landing page and clients open in the Servicing View.</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -17306,16 +16597,15 @@
           <t>The Customer Search is the landing page and clients open in the Servicing View.</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -17350,19 +16640,18 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Customer Service Facility is not in the menu; /csf shows the no-access page.</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="27" t="inlineStr">
+          <t>Customer Service Facility is not in the menu; its address shows the no-access page.</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -17397,19 +16686,18 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Customer Service Facility is not in the menu; /csf shows the no-access page.</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
+          <t>Customer Service Facility is not in the menu; its address shows the no-access page.</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -17447,16 +16735,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -17494,16 +16781,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -17538,19 +16824,18 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Update Contact is not shown; the contact update call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+          <t>Update Contact is not shown; a direct contact update request is refused.</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -17585,19 +16870,18 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Update Contact is not shown; the contact update call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+          <t>Update Contact is not shown; a direct contact update request is refused.</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -17635,16 +16919,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -17682,16 +16965,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -17726,19 +17008,18 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Resend is not shown; the resend call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+          <t>Resend is not shown; a direct resend request is refused.</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -17776,16 +17057,15 @@
           <t>The recipient field is editable and the reason is asked.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -17820,19 +17100,18 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>The recipient is read only; a call with another recipient returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+          <t>The recipient is read only; a direct request with another recipient is refused.</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -17867,19 +17146,18 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>The recipient is read only; a call with another recipient returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+          <t>The recipient is read only; a direct request with another recipient is refused.</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -17917,16 +17195,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -17964,16 +17241,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -18008,19 +17284,18 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Upload is not shown; the upload call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="27" t="inlineStr">
+          <t>Upload is not shown; a direct upload request is refused.</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -18058,16 +17333,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -18105,16 +17379,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="27" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -18149,19 +17422,18 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Documents cannot be opened or downloaded; the download call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr">
+          <t>Documents cannot be opened or downloaded; a direct download request is refused.</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -18199,16 +17471,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -18246,16 +17517,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -18290,19 +17560,18 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>The Customer Service category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+          <t>The Customer Service category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -18337,19 +17606,18 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>The Customer Service category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="27" t="inlineStr">
+          <t>The Customer Service category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -18387,16 +17655,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -18434,16 +17701,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="27" t="inlineStr">
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -18478,19 +17744,18 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Audit Trail is not in the menu; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="27" t="inlineStr">
+          <t>Audit Trail is not in the menu; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -18525,19 +17790,18 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Audit Trail is not in the menu; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+          <t>Audit Trail is not in the menu; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -18575,16 +17839,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -18619,19 +17882,18 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; Users is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+          <t>Administration &gt; Users is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -18666,19 +17928,18 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; Users is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr">
+          <t>Administration &gt; Users is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -18713,26 +17974,25 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; Users is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr">
+          <t>Administration &gt; Users is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M37"/>
+  <autoFilter ref="A4:L37"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I537">
+  <conditionalFormatting sqref="H5:H537">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -18746,7 +18006,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M537">
+  <conditionalFormatting sqref="A5:L537">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -18755,7 +18015,7 @@
     <dataValidation sqref="F5:F537" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I537" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H537" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Drop-1_Transactional/BRD-09_Customer_Servicing_Facility/BIBS_TestPlan_BRD-09_Customer_Servicing_Facility_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-09_Customer_Servicing_Facility/BIBS_TestPlan_BRD-09_Customer_Servicing_Facility_v1.0.xlsx
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Every outbox row keeps its payload so the outbox can be replayed.</t>
+          <t>Every change waiting in the outbox keeps its content so it can be sent again.</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>The database log is archived at least every 15 minutes, and a daily base backup runs outside the peak hours.</t>
+          <t>The changes are saved to the backup storage at least every 15 minutes, and a daily full backup runs outside the peak hours.</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>A restore recovers the database to a point less than 15 minutes before the test.</t>
+          <t>A restore recovers BIBS data to a point less than 15 minutes before the test.</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Online response times stay within the targets while the log is archived.</t>
+          <t>Online response times stay within the targets while the changes are saved.</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>INFRA – Infrastructure team (database administrator)</t>
+          <t>INFRA – Infrastructure team (infrastructure administrator)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -6110,8 +6110,8 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>The third wrong attempt locks the account; the correct password is then refused.
-Message "Account is locked. Contact your administrator.".</t>
+          <t>The third wrong attempt locks the account; the correct password is then refused with the same message as a wrong password; the lock shows to the System Administrator in Administration &gt; Users.
+Message "Invalid user name or password".</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>A PASSED verification of TD-CSF-02 was recorded 29 minutes ago (the test lead sets the time in the test database, or the tester waits).
+          <t>A PASSED verification of TD-CSF-02 was recorded 29 minutes ago (the test lead sets the time in the test environment, or the tester waits).
 Data: TD-CSF-02 Client with CBG and non-CBG accounts; TD-CSF-09 Parameters as configured</t>
         </is>
       </c>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I60" s="12" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Outbox rows keep the payload for replay</t>
+          <t>Changes in the outbox keep their content to be sent again</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Archive interval and base backup schedule</t>
+          <t>Backup interval and full backup schedule</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -13927,24 +13927,24 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>INFRA – Infrastructure team (database administrator)</t>
+          <t>INFRA – Infrastructure team (infrastructure administrator)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Database restore environment (infrastructure console)</t>
+          <t>Restore environment of the infrastructure team</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr"/>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>1. Read the archive interval of the database and the backup schedule.
-2. List the archived log segments of the last two hours.</t>
+          <t>1. Read the backup interval of the changes and the backup schedule.
+2. List the saved changes of the last two hours in the backup storage.</t>
         </is>
       </c>
       <c r="K117" s="12" t="inlineStr">
         <is>
-          <t>The archive interval is 15 minutes or less; at least one segment is archived in every 15-minute window; the daily base backup runs outside 10:00-12:00 and 14:00-16:00.</t>
+          <t>The backup interval is 15 minutes or less; changes are saved in every 15-minute window; the daily full backup runs outside 10:00-12:00 and 14:00-16:00.</t>
         </is>
       </c>
       <c r="L117" s="12" t="inlineStr">
@@ -13995,25 +13995,25 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>INFRA – Infrastructure team (database administrator)</t>
+          <t>INFRA – Infrastructure team (infrastructure administrator)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>Database restore environment (infrastructure console)</t>
+          <t>Restore environment of the infrastructure team</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr"/>
       <c r="J118" s="12" t="inlineStr">
         <is>
           <t>1. Note the time T; make a contact change on SIT at T minus 20 minutes and another at T minus 5 minutes.
-2. Restore the last base backup and the archived log on the restore environment up to the latest point.
+2. Restore the last full backup and the saved changes on the restore environment up to the latest point.
 3. Check the two contact changes.</t>
         </is>
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>The restored database holds the change made at T minus 20 minutes and is recovered to a point less than 15 minutes before T.</t>
+          <t>The restored data holds the change made at T minus 20 minutes and is recovered to a point less than 15 minutes before T.</t>
         </is>
       </c>
       <c r="L118" s="12" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>INFRA – Infrastructure team (database administrator)</t>
+          <t>INFRA – Infrastructure team (infrastructure administrator)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>Database restore environment (infrastructure console)</t>
+          <t>Restore environment of the infrastructure team</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr"/>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Keyed in Cashiering (BRD-2) on SIT by the test lead; receipt dates set in the test database</t>
+          <t>Keyed in Cashiering (BRD-2) on SIT by the test lead; receipt dates set in the test environment</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
